--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19904E6-5E78-4584-85C2-19632C8453B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAD87E7-8D77-4852-ADEB-ABC7B6C2B7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,12 @@
   </si>
   <si>
     <t>completed pending work</t>
+  </si>
+  <si>
+    <t>GOOD</t>
+  </si>
+  <si>
+    <t>learning new things.</t>
   </si>
 </sst>
 </file>
@@ -2100,26 +2106,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B28" s="14">
+        <v>350</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>80</v>
+      </c>
+      <c r="E28" s="14">
+        <v>50</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>400</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAD87E7-8D77-4852-ADEB-ABC7B6C2B7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC34D8C-209F-4977-850C-D8F87C9F20F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,12 @@
   </si>
   <si>
     <t>learning new things.</t>
+  </si>
+  <si>
+    <t>SATISFIED</t>
+  </si>
+  <si>
+    <t>it was a good day</t>
   </si>
 </sst>
 </file>
@@ -2152,26 +2158,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B29" s="14">
+        <v>400</v>
+      </c>
+      <c r="C29" s="14">
+        <v>50</v>
+      </c>
+      <c r="D29" s="14">
+        <v>70</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>150</v>
+      </c>
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="14">
+        <v>400</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC34D8C-209F-4977-850C-D8F87C9F20F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE2E297-D04F-40F8-942B-50F1FAF33322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>it was a good day</t>
+  </si>
+  <si>
+    <t>ca went good</t>
   </si>
 </sst>
 </file>
@@ -2204,26 +2207,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B30" s="14">
+        <v>350</v>
+      </c>
+      <c r="C30" s="14">
+        <v>100</v>
+      </c>
+      <c r="D30" s="14">
+        <v>80</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>200</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE2E297-D04F-40F8-942B-50F1FAF33322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A642340D-8032-4A61-85F1-564941B5E5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>ca went good</t>
+  </si>
+  <si>
+    <t>it wasa hectic day</t>
   </si>
 </sst>
 </file>
@@ -2253,26 +2256,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B31" s="14">
+        <v>400</v>
+      </c>
+      <c r="C31" s="14">
+        <v>90</v>
+      </c>
+      <c r="D31" s="14">
+        <v>50</v>
+      </c>
+      <c r="E31" s="14">
+        <v>40</v>
+      </c>
+      <c r="F31" s="14">
+        <v>200</v>
+      </c>
+      <c r="G31" s="14">
+        <v>4</v>
+      </c>
+      <c r="H31" s="14">
+        <v>250</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A642340D-8032-4A61-85F1-564941B5E5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57DBD71-B3E3-4529-8436-7532A9826FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -329,6 +329,21 @@
   </si>
   <si>
     <t>it wasa hectic day</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>first time participated in events</t>
+  </si>
+  <si>
+    <t>avverage</t>
+  </si>
+  <si>
+    <t>exploring new things</t>
   </si>
 </sst>
 </file>
@@ -2302,48 +2317,96 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B32" s="14">
+        <v>300</v>
+      </c>
+      <c r="C32" s="14">
+        <v>100</v>
+      </c>
+      <c r="D32" s="14">
+        <v>150</v>
+      </c>
+      <c r="E32" s="14">
+        <v>90</v>
+      </c>
+      <c r="F32" s="14">
+        <v>350</v>
+      </c>
+      <c r="G32" s="14">
+        <v>7</v>
+      </c>
+      <c r="H32" s="14">
+        <v>200</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B33" s="14">
+        <v>300</v>
+      </c>
+      <c r="C33" s="14">
+        <v>100</v>
+      </c>
+      <c r="D33" s="14">
+        <v>90</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>350</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+      <c r="H33" s="14">
+        <v>150</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57DBD71-B3E3-4529-8436-7532A9826FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B346F2B-2DE1-467D-B78E-80F0195A82B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,18 @@
   </si>
   <si>
     <t>exploring new things</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>finally weekends</t>
+  </si>
+  <si>
+    <t>happy</t>
+  </si>
+  <si>
+    <t>shopping day</t>
   </si>
 </sst>
 </file>
@@ -2409,48 +2421,96 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B34" s="14">
+        <v>350</v>
+      </c>
+      <c r="C34" s="14">
+        <v>100</v>
+      </c>
+      <c r="D34" s="14">
+        <v>60</v>
+      </c>
+      <c r="E34" s="14">
+        <v>50</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>200</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>680</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B35" s="14">
+        <v>400</v>
+      </c>
+      <c r="C35" s="14">
+        <v>100</v>
+      </c>
+      <c r="D35" s="14">
+        <v>80</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>400</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B346F2B-2DE1-467D-B78E-80F0195A82B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352AA4E7-E2CF-4E12-9B5D-621DEB659D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>shopping day</t>
+  </si>
+  <si>
+    <t>something hit hard today</t>
   </si>
 </sst>
 </file>
@@ -2513,26 +2516,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B36" s="14">
+        <v>400</v>
+      </c>
+      <c r="C36" s="14">
+        <v>150</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>20</v>
+      </c>
+      <c r="F36" s="14">
+        <v>150</v>
+      </c>
+      <c r="G36" s="14">
+        <v>3</v>
+      </c>
+      <c r="H36" s="14">
+        <v>320</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352AA4E7-E2CF-4E12-9B5D-621DEB659D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1538F31F-F873-415B-B834-88AB74B38BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>something hit hard today</t>
+  </si>
+  <si>
+    <t>happy dat</t>
   </si>
 </sst>
 </file>
@@ -2562,26 +2565,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B37" s="14">
+        <v>250</v>
+      </c>
+      <c r="C37" s="14">
+        <v>200</v>
+      </c>
+      <c r="D37" s="14">
+        <v>180</v>
+      </c>
+      <c r="E37" s="14">
+        <v>50</v>
+      </c>
+      <c r="F37" s="14">
+        <v>360</v>
+      </c>
+      <c r="G37" s="14">
+        <v>6</v>
+      </c>
+      <c r="H37" s="14">
+        <v>200</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1538F31F-F873-415B-B834-88AB74B38BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA52A08D-7D99-461B-9D0E-F82973C2D3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -362,6 +362,12 @@
   </si>
   <si>
     <t>happy dat</t>
+  </si>
+  <si>
+    <t>I prepared for english CA and also started with mid term preparations.</t>
+  </si>
+  <si>
+    <t>Today Ca went good,also I started working on my minor project</t>
   </si>
 </sst>
 </file>
@@ -2610,49 +2616,97 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+    <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B38" s="14">
+        <v>250</v>
+      </c>
+      <c r="C38" s="14">
+        <v>150</v>
+      </c>
+      <c r="D38" s="14">
+        <v>250</v>
+      </c>
+      <c r="E38" s="14">
+        <v>50</v>
+      </c>
+      <c r="F38" s="14">
+        <v>360</v>
+      </c>
+      <c r="G38" s="14">
+        <v>6</v>
+      </c>
+      <c r="H38" s="14">
+        <v>150</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+        <v>230</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B39" s="14">
+        <v>400</v>
+      </c>
+      <c r="C39" s="14">
+        <v>100</v>
+      </c>
+      <c r="D39" s="14">
+        <v>200</v>
+      </c>
+      <c r="E39" s="14">
+        <v>60</v>
+      </c>
+      <c r="F39" s="14">
+        <v>350</v>
+      </c>
+      <c r="G39" s="14">
+        <v>7</v>
+      </c>
+      <c r="H39" s="14">
+        <v>200</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA52A08D-7D99-461B-9D0E-F82973C2D3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B56550-E357-43EF-990B-07A3AA205955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -368,6 +368,12 @@
   </si>
   <si>
     <t>Today Ca went good,also I started working on my minor project</t>
+  </si>
+  <si>
+    <t>tgood</t>
+  </si>
+  <si>
+    <t>I made roadmapp for my mid terms exam.</t>
   </si>
 </sst>
 </file>
@@ -2708,27 +2714,51 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B40" s="14">
+        <v>400</v>
+      </c>
+      <c r="C40" s="14">
+        <v>120</v>
+      </c>
+      <c r="D40" s="14">
+        <v>250</v>
+      </c>
+      <c r="E40" s="14">
+        <v>50</v>
+      </c>
+      <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>150</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B56550-E357-43EF-990B-07A3AA205955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECA83FC-62E6-4167-8CA7-D705D33C7C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -374,6 +374,15 @@
   </si>
   <si>
     <t>I made roadmapp for my mid terms exam.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Today finally I completed my python minor project and started with mid termspreparation.</t>
   </si>
 </sst>
 </file>
@@ -2760,27 +2769,51 @@
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+    <row r="41" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B41" s="14">
+        <v>500</v>
+      </c>
+      <c r="C41" s="14">
+        <v>100</v>
+      </c>
+      <c r="D41" s="14">
+        <v>250</v>
+      </c>
+      <c r="E41" s="14">
+        <v>150</v>
+      </c>
+      <c r="F41" s="14">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>200</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECA83FC-62E6-4167-8CA7-D705D33C7C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6768477-E359-40B3-A5F7-6095A74C25DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="117">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -383,6 +383,9 @@
   </si>
   <si>
     <t>Today finally I completed my python minor project and started with mid termspreparation.</t>
+  </si>
+  <si>
+    <t>whats going on university doesn’t making feel good.Justice should be taken but not in such manner.</t>
   </si>
 </sst>
 </file>
@@ -2815,27 +2818,51 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+    <row r="42" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B42" s="14">
+        <v>500</v>
+      </c>
+      <c r="C42" s="14">
+        <v>120</v>
+      </c>
+      <c r="D42" s="14">
+        <v>300</v>
+      </c>
+      <c r="E42" s="14">
+        <v>50</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>250</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6768477-E359-40B3-A5F7-6095A74C25DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F198DB1E-6D69-43C5-BB37-1D8D0B352CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>whats going on university doesn’t making feel good.Justice should be taken but not in such manner.</t>
+  </si>
+  <si>
+    <t>Decided to do a python and c++ course in 10 days leave.</t>
   </si>
 </sst>
 </file>
@@ -2864,27 +2867,51 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+    <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B43" s="14">
+        <v>600</v>
+      </c>
+      <c r="C43" s="14">
+        <v>150</v>
+      </c>
+      <c r="D43" s="14">
+        <v>350</v>
+      </c>
+      <c r="E43" s="14">
+        <v>100</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>200</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F198DB1E-6D69-43C5-BB37-1D8D0B352CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E88675E-045D-416C-B864-64C4DC23346F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="120">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,6 +389,12 @@
   </si>
   <si>
     <t>Decided to do a python and c++ course in 10 days leave.</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Not well today.</t>
   </si>
 </sst>
 </file>
@@ -2914,26 +2920,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B44" s="14">
+        <v>650</v>
+      </c>
+      <c r="C44" s="14">
+        <v>50</v>
+      </c>
+      <c r="D44" s="14">
+        <v>150</v>
+      </c>
+      <c r="E44" s="14">
+        <v>50</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>400</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E88675E-045D-416C-B864-64C4DC23346F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC67478D-8446-4D13-9FF9-7D27368D0BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="122">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -395,6 +395,12 @@
   </si>
   <si>
     <t>Not well today.</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>I started preparing for mid terms exams</t>
   </si>
 </sst>
 </file>
@@ -2965,27 +2971,51 @@
         <v>119</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+    <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B45" s="14">
+        <v>500</v>
+      </c>
+      <c r="C45" s="14">
+        <v>100</v>
+      </c>
+      <c r="D45" s="14">
+        <v>400</v>
+      </c>
+      <c r="E45" s="14">
+        <v>50</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>250</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC67478D-8446-4D13-9FF9-7D27368D0BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397BEE88-CA7F-4CEF-B46B-4059E3A21109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="123">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>I started preparing for mid terms exams</t>
+  </si>
+  <si>
+    <t>This 10 days holiday gave us time to prepare for mid terms and complete all our pending task,but yes missing university days.</t>
   </si>
 </sst>
 </file>
@@ -3017,27 +3020,51 @@
         <v>121</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+    <row r="46" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A46" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B46" s="14">
+        <v>400</v>
+      </c>
+      <c r="C46" s="14">
+        <v>100</v>
+      </c>
+      <c r="D46" s="14">
+        <v>500</v>
+      </c>
+      <c r="E46" s="14">
+        <v>20</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>200</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397BEE88-CA7F-4CEF-B46B-4059E3A21109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767D4584-AE15-40FC-B1F0-6C682F644BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="124">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>This 10 days holiday gave us time to prepare for mid terms and complete all our pending task,but yes missing university days.</t>
+  </si>
+  <si>
+    <t>Today I started with my analytical skills mid term syllabus.</t>
   </si>
 </sst>
 </file>
@@ -3066,27 +3069,51 @@
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+    <row r="47" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B47" s="14">
+        <v>400</v>
+      </c>
+      <c r="C47" s="14">
+        <v>100</v>
+      </c>
+      <c r="D47" s="14">
+        <v>550</v>
+      </c>
+      <c r="E47" s="14">
+        <v>60</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>200</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767D4584-AE15-40FC-B1F0-6C682F644BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE69299-205C-4578-B03E-114667B548BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="125">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -407,6 +407,9 @@
   </si>
   <si>
     <t>Today I started with my analytical skills mid term syllabus.</t>
+  </si>
+  <si>
+    <t>I completed analytical skill unit 3 today.</t>
   </si>
 </sst>
 </file>
@@ -3115,27 +3118,51 @@
         <v>123</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B48" s="14">
+        <v>400</v>
+      </c>
+      <c r="C48" s="14">
+        <v>120</v>
+      </c>
+      <c r="D48" s="14">
+        <v>500</v>
+      </c>
+      <c r="E48" s="14">
+        <v>40</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>300</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE69299-205C-4578-B03E-114667B548BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5FA685-AB8F-413E-9C0E-3F92C74D11AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="126">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -410,6 +410,9 @@
   </si>
   <si>
     <t>I completed analytical skill unit 3 today.</t>
+  </si>
+  <si>
+    <t>My shopping day and studied also for mid terms</t>
   </si>
 </sst>
 </file>
@@ -3164,27 +3167,51 @@
         <v>124</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+    <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B49" s="14">
+        <v>400</v>
+      </c>
+      <c r="C49" s="14">
+        <v>100</v>
+      </c>
+      <c r="D49" s="14">
+        <v>500</v>
+      </c>
+      <c r="E49" s="14">
+        <v>60</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>300</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5FA685-AB8F-413E-9C0E-3F92C74D11AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F463AFF-8601-4B85-8C41-48DD4E835200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="127">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -413,6 +413,9 @@
   </si>
   <si>
     <t>My shopping day and studied also for mid terms</t>
+  </si>
+  <si>
+    <t>Started with C++ preparation tooday.</t>
   </si>
 </sst>
 </file>
@@ -3213,27 +3216,51 @@
         <v>125</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B50" s="14">
+        <v>300</v>
+      </c>
+      <c r="C50" s="14">
+        <v>150</v>
+      </c>
+      <c r="D50" s="14">
+        <v>400</v>
+      </c>
+      <c r="E50" s="14">
+        <v>40</v>
+      </c>
+      <c r="F50" s="14">
+        <v>150</v>
+      </c>
+      <c r="G50" s="14">
+        <v>3</v>
+      </c>
+      <c r="H50" s="14">
+        <v>300</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F463AFF-8601-4B85-8C41-48DD4E835200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68E7C21-BEE4-42C9-8029-D87DF50B6CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,19 +211,10 @@
     <t>Did my favourite task:Shopping.</t>
   </si>
   <si>
-    <t>Average</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
     <t>Plannned something but didn’t happened according to plan.</t>
-  </si>
-  <si>
-    <t>Haapy</t>
-  </si>
-  <si>
-    <t>satisfied</t>
   </si>
   <si>
     <t>Low</t>
@@ -235,25 +226,13 @@
     <t>nothing today.</t>
   </si>
   <si>
-    <t>Hectic</t>
-  </si>
-  <si>
-    <t>very low</t>
-  </si>
-  <si>
     <t>just realized that how life become hard in early 20's.</t>
-  </si>
-  <si>
-    <t>medium</t>
   </si>
   <si>
     <t xml:space="preserve">I didn’t like the behaviour of one of my friend towards me </t>
   </si>
   <si>
     <t>U cant do everything in a single day.</t>
-  </si>
-  <si>
-    <t>Stisfied</t>
   </si>
   <si>
     <t>Weekend are my fav.</t>
@@ -265,31 +244,16 @@
     <t>Had a nice conversation with my classmate.</t>
   </si>
   <si>
-    <t>not satisfied</t>
-  </si>
-  <si>
     <t>my CA doesn’t go well not satisfied with  the presentation I gave.</t>
   </si>
   <si>
     <t>I realised something about me today</t>
   </si>
   <si>
-    <t>Tired</t>
-  </si>
-  <si>
-    <t>low</t>
-  </si>
-  <si>
     <t>Learn new things.</t>
   </si>
   <si>
     <t>no holiday on weekend.</t>
-  </si>
-  <si>
-    <t>good</t>
-  </si>
-  <si>
-    <t>high</t>
   </si>
   <si>
     <t>preparing for ca</t>
@@ -304,22 +268,13 @@
     <t>learn new things.</t>
   </si>
   <si>
-    <t>tired</t>
-  </si>
-  <si>
     <t>not well today</t>
   </si>
   <si>
     <t>completed pending work</t>
   </si>
   <si>
-    <t>GOOD</t>
-  </si>
-  <si>
     <t>learning new things.</t>
-  </si>
-  <si>
-    <t>SATISFIED</t>
   </si>
   <si>
     <t>it was a good day</t>
@@ -331,28 +286,13 @@
     <t>it wasa hectic day</t>
   </si>
   <si>
-    <t>AVERAGE</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>first time participated in events</t>
-  </si>
-  <si>
-    <t>avverage</t>
   </si>
   <si>
     <t>exploring new things</t>
   </si>
   <si>
-    <t>average</t>
-  </si>
-  <si>
     <t>finally weekends</t>
-  </si>
-  <si>
-    <t>happy</t>
   </si>
   <si>
     <t>shopping day</t>
@@ -368,9 +308,6 @@
   </si>
   <si>
     <t>Today Ca went good,also I started working on my minor project</t>
-  </si>
-  <si>
-    <t>tgood</t>
   </si>
   <si>
     <t>I made roadmapp for my mid terms exam.</t>
@@ -416,6 +353,15 @@
   </si>
   <si>
     <t>Started with C++ preparation tooday.</t>
+  </si>
+  <si>
+    <t>Today again I continu with my c++ preparation.Sylllabus is to much and time is less.</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1320,16 +1266,16 @@
         <v>500</v>
       </c>
       <c r="K8" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="N8" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1369,13 +1315,13 @@
         <v>49</v>
       </c>
       <c r="L9" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1412,16 +1358,16 @@
         <v>250</v>
       </c>
       <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N10" s="17" t="s">
         <v>61</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1458,16 +1404,16 @@
         <v>470</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1507,13 +1453,13 @@
         <v>49</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1553,13 +1499,13 @@
         <v>49</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1599,13 +1545,13 @@
         <v>49</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>55</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1648,10 +1594,10 @@
         <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1691,13 +1637,13 @@
         <v>49</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1737,13 +1683,13 @@
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="M17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1780,16 +1726,16 @@
         <v>280</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="L18" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1826,16 +1772,16 @@
         <v>390</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1872,16 +1818,16 @@
         <v>290</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1918,16 +1864,16 @@
         <v>490</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1970,10 +1916,10 @@
         <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -2010,16 +1956,16 @@
         <v>400</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -2056,16 +2002,16 @@
         <v>160</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2102,16 +2048,16 @@
         <v>365</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2148,13 +2094,13 @@
         <v>350</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="N26" s="17"/>
     </row>
@@ -2192,16 +2138,16 @@
         <v>810</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2238,16 +2184,16 @@
         <v>560</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2284,16 +2230,16 @@
         <v>340</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2330,16 +2276,16 @@
         <v>400</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2376,16 +2322,16 @@
         <v>410</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2422,16 +2368,16 @@
         <v>250</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2468,16 +2414,16 @@
         <v>390</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2514,16 +2460,16 @@
         <v>680</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -2560,16 +2506,16 @@
         <v>400</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -2606,16 +2552,16 @@
         <v>280</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -2652,16 +2598,16 @@
         <v>200</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2698,16 +2644,16 @@
         <v>230</v>
       </c>
       <c r="K38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N38" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="L38" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="M38" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="N38" s="17" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2744,16 +2690,16 @@
         <v>130</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2790,16 +2736,16 @@
         <v>120</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2836,16 +2782,16 @@
         <v>240</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="M41" s="16" t="s">
         <v>55</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2888,10 +2834,10 @@
         <v>50</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2931,13 +2877,13 @@
         <v>49</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="M43" s="16" t="s">
         <v>55</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -2974,16 +2920,16 @@
         <v>140</v>
       </c>
       <c r="K44" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L44" s="16" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="M44" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3023,13 +2969,13 @@
         <v>49</v>
       </c>
       <c r="L45" s="16" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="M45" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N45" s="17" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -3066,7 +3012,7 @@
         <v>220</v>
       </c>
       <c r="K46" s="16" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="L46" s="16" t="s">
         <v>50</v>
@@ -3075,7 +3021,7 @@
         <v>55</v>
       </c>
       <c r="N46" s="17" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -3121,7 +3067,7 @@
         <v>55</v>
       </c>
       <c r="N47" s="17" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3161,13 +3107,13 @@
         <v>49</v>
       </c>
       <c r="L48" s="16" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="M48" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N48" s="17" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3204,16 +3150,16 @@
         <v>80</v>
       </c>
       <c r="K49" s="16" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="L49" s="16" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="M49" s="16" t="s">
         <v>55</v>
       </c>
       <c r="N49" s="17" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3250,39 +3196,63 @@
         <v>100</v>
       </c>
       <c r="K50" s="16" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="L50" s="16" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="M50" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N50" s="17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B51" s="14">
+        <v>350</v>
+      </c>
+      <c r="C51" s="14">
+        <v>100</v>
+      </c>
+      <c r="D51" s="14">
+        <v>450</v>
+      </c>
+      <c r="E51" s="14">
+        <v>40</v>
+      </c>
+      <c r="F51" s="14">
+        <v>250</v>
+      </c>
+      <c r="G51" s="14">
+        <v>5</v>
+      </c>
+      <c r="H51" s="14">
+        <v>200</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68E7C21-BEE4-42C9-8029-D87DF50B6CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8EE023-33C2-4960-9F9F-1B78BA4DC216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Still my c++ is going on .</t>
   </si>
 </sst>
 </file>
@@ -3255,26 +3258,50 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B52" s="14">
+        <v>350</v>
+      </c>
+      <c r="C52" s="14">
+        <v>60</v>
+      </c>
+      <c r="D52" s="14">
+        <v>450</v>
+      </c>
+      <c r="E52" s="14">
+        <v>60</v>
+      </c>
+      <c r="F52" s="14">
+        <v>350</v>
+      </c>
+      <c r="G52" s="14">
+        <v>7</v>
+      </c>
+      <c r="H52" s="14">
+        <v>100</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8EE023-33C2-4960-9F9F-1B78BA4DC216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5D3A39-F25A-40CD-8198-C99FB45D6957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>Still my c++ is going on .</t>
+  </si>
+  <si>
+    <t>Today I started with data communication and networking mid term preparations.</t>
   </si>
 </sst>
 </file>
@@ -3303,27 +3306,51 @@
         <v>109</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+    <row r="53" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B53" s="14">
+        <v>400</v>
+      </c>
+      <c r="C53" s="14">
+        <v>70</v>
+      </c>
+      <c r="D53" s="14">
+        <v>450</v>
+      </c>
+      <c r="E53" s="14">
+        <v>60</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>150</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5D3A39-F25A-40CD-8198-C99FB45D6957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98005E0-6AE8-4078-9009-387F93DD1948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>Today I started with data communication and networking mid term preparations.</t>
+  </si>
+  <si>
+    <t>Mid terms preparation is going on .</t>
   </si>
 </sst>
 </file>
@@ -3352,27 +3355,51 @@
         <v>110</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+    <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B54" s="14">
+        <v>300</v>
+      </c>
+      <c r="C54" s="14">
+        <v>80</v>
+      </c>
+      <c r="D54" s="14">
+        <v>600</v>
+      </c>
+      <c r="E54" s="14">
+        <v>80</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>350</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98005E0-6AE8-4078-9009-387F93DD1948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F966A9-D3F3-4CE5-9B78-83B96724A2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>Mid terms preparation is going on .</t>
+  </si>
+  <si>
+    <t>Today I completed with my networking mid term preparation.</t>
   </si>
 </sst>
 </file>
@@ -3401,27 +3404,51 @@
         <v>111</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+    <row r="55" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B55" s="14">
+        <v>350</v>
+      </c>
+      <c r="C55" s="14">
+        <v>90</v>
+      </c>
+      <c r="D55" s="14">
+        <v>500</v>
+      </c>
+      <c r="E55" s="14">
+        <v>60</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>400</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F966A9-D3F3-4CE5-9B78-83B96724A2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB89EFE-A1CE-4B8C-9B63-51E996D00CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -374,6 +374,12 @@
   </si>
   <si>
     <t>Today I completed with my networking mid term preparation.</t>
+  </si>
+  <si>
+    <t>Today I revise mid term and went for outing.</t>
+  </si>
+  <si>
+    <t>Today I give my first exam in university and it went good.</t>
   </si>
 </sst>
 </file>
@@ -3450,49 +3456,97 @@
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+    <row r="56" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B56" s="14">
+        <v>200</v>
+      </c>
+      <c r="C56" s="14">
+        <v>80</v>
+      </c>
+      <c r="D56" s="14">
+        <v>500</v>
+      </c>
+      <c r="E56" s="14">
+        <v>60</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>400</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+        <v>200</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B57" s="14">
+        <v>200</v>
+      </c>
+      <c r="C57" s="14">
+        <v>120</v>
+      </c>
+      <c r="D57" s="14">
+        <v>500</v>
+      </c>
+      <c r="E57" s="14">
+        <v>90</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>500</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB89EFE-A1CE-4B8C-9B63-51E996D00CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DBD4D7-B134-467D-8343-C5595BDBC84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>Today I give my first exam in university and it went good.</t>
+  </si>
+  <si>
+    <t>Today I done with my second mid term and it went good</t>
   </si>
 </sst>
 </file>
@@ -3548,27 +3551,51 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+    <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B58" s="14">
+        <v>200</v>
+      </c>
+      <c r="C58" s="14">
+        <v>120</v>
+      </c>
+      <c r="D58" s="14">
+        <v>550</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>450</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DBD4D7-B134-467D-8343-C5595BDBC84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85285C5A-EAF9-4013-811E-2B3454425E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="117">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -383,6 +383,9 @@
   </si>
   <si>
     <t>Today I done with my second mid term and it went good</t>
+  </si>
+  <si>
+    <t>Dbms mid term also went good.</t>
   </si>
 </sst>
 </file>
@@ -3598,26 +3601,50 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B59" s="14">
+        <v>400</v>
+      </c>
+      <c r="C59" s="14">
+        <v>200</v>
+      </c>
+      <c r="D59" s="14">
+        <v>400</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>300</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85285C5A-EAF9-4013-811E-2B3454425E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D6B6C6-10D3-45EC-BADA-7388CB1E1667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>Dbms mid term also went good.</t>
+  </si>
+  <si>
+    <t>I studied analytical skills as tmrw I have mid term.</t>
   </si>
 </sst>
 </file>
@@ -3646,27 +3649,51 @@
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+    <row r="60" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="14">
+        <v>500</v>
+      </c>
+      <c r="C60" s="14">
+        <v>100</v>
+      </c>
+      <c r="D60" s="14">
+        <v>400</v>
+      </c>
+      <c r="E60" s="14">
+        <v>0</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>200</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D6B6C6-10D3-45EC-BADA-7388CB1E1667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1B9EFD-99E5-47D3-BF1C-98BE9AD56488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="119">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,6 +389,9 @@
   </si>
   <si>
     <t>I studied analytical skills as tmrw I have mid term.</t>
+  </si>
+  <si>
+    <t>Today my analytical mid term doesn’t well good.</t>
   </si>
 </sst>
 </file>
@@ -3695,27 +3698,51 @@
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+    <row r="61" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="14">
+        <v>400</v>
+      </c>
+      <c r="C61" s="14">
+        <v>150</v>
+      </c>
+      <c r="D61" s="14">
+        <v>200</v>
+      </c>
+      <c r="E61" s="14">
+        <v>0</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>400</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1B9EFD-99E5-47D3-BF1C-98BE9AD56488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3B968B-8D38-4769-BFB2-23923BF77912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="121">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -392,6 +392,12 @@
   </si>
   <si>
     <t>Today my analytical mid term doesn’t well good.</t>
+  </si>
+  <si>
+    <t>Last Mid term exam today and it went good.</t>
+  </si>
+  <si>
+    <t>Today I just relaxed enjoyed my Sunday .</t>
   </si>
 </sst>
 </file>
@@ -3744,49 +3750,97 @@
         <v>118</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+    <row r="62" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="14">
+        <v>400</v>
+      </c>
+      <c r="C62" s="14">
+        <v>200</v>
+      </c>
+      <c r="D62" s="14">
+        <v>150</v>
+      </c>
+      <c r="E62" s="14">
+        <v>150</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>400</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+        <v>140</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="14">
+        <v>500</v>
+      </c>
+      <c r="C63" s="14">
+        <v>200</v>
+      </c>
+      <c r="D63" s="14">
+        <v>0</v>
+      </c>
+      <c r="E63" s="14">
+        <v>120</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>300</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3B968B-8D38-4769-BFB2-23923BF77912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6A75B3-1C79-4633-995D-10E8F452838D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="122">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -398,6 +398,9 @@
   </si>
   <si>
     <t>Today I just relaxed enjoyed my Sunday .</t>
+  </si>
+  <si>
+    <t>Today after 15 days regular classses started.</t>
   </si>
 </sst>
 </file>
@@ -3842,27 +3845,51 @@
         <v>120</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+    <row r="64" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="14">
+        <v>400</v>
+      </c>
+      <c r="C64" s="14">
+        <v>250</v>
+      </c>
+      <c r="D64" s="14">
+        <v>90</v>
+      </c>
+      <c r="E64" s="14">
+        <v>60</v>
+      </c>
+      <c r="F64" s="14">
+        <v>150</v>
+      </c>
+      <c r="G64" s="14">
+        <v>3</v>
+      </c>
+      <c r="H64" s="14">
+        <v>350</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6A75B3-1C79-4633-995D-10E8F452838D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DE66E2-FF22-45E5-96E1-2BF9CDC0C942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="123">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>Today after 15 days regular classses started.</t>
+  </si>
+  <si>
+    <t>Celebrated dushera .</t>
   </si>
 </sst>
 </file>
@@ -3892,26 +3895,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="14">
+        <v>500</v>
+      </c>
+      <c r="C65" s="14">
+        <v>180</v>
+      </c>
+      <c r="D65" s="14">
+        <v>90</v>
+      </c>
+      <c r="E65" s="14">
+        <v>120</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>400</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DE66E2-FF22-45E5-96E1-2BF9CDC0C942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0588E3-9E94-46E8-AF99-2A7E93F6DF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="124">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>Celebrated dushera .</t>
+  </si>
+  <si>
+    <t>I attended lecture and did revision analytical skills.</t>
   </si>
 </sst>
 </file>
@@ -3940,27 +3943,51 @@
         <v>122</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+    <row r="66" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="14">
+        <v>500</v>
+      </c>
+      <c r="C66" s="14">
+        <v>150</v>
+      </c>
+      <c r="D66" s="14">
+        <v>120</v>
+      </c>
+      <c r="E66" s="14">
+        <v>50</v>
+      </c>
+      <c r="F66" s="14">
+        <v>350</v>
+      </c>
+      <c r="G66" s="14">
+        <v>6</v>
+      </c>
+      <c r="H66" s="14">
+        <v>150</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0588E3-9E94-46E8-AF99-2A7E93F6DF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D092AE25-D4A1-42E6-AE15-11834C51FC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="125">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -407,6 +407,9 @@
   </si>
   <si>
     <t>I attended lecture and did revision analytical skills.</t>
+  </si>
+  <si>
+    <t>Today I went for blood donation camp to donate blood.</t>
   </si>
 </sst>
 </file>
@@ -3989,27 +3992,51 @@
         <v>123</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+    <row r="67" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="14">
+        <v>400</v>
+      </c>
+      <c r="C67" s="14">
+        <v>120</v>
+      </c>
+      <c r="D67" s="14">
+        <v>120</v>
+      </c>
+      <c r="E67" s="14">
+        <v>60</v>
+      </c>
+      <c r="F67" s="14">
+        <v>250</v>
+      </c>
+      <c r="G67" s="14">
+        <v>5</v>
+      </c>
+      <c r="H67" s="14">
+        <v>300</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D092AE25-D4A1-42E6-AE15-11834C51FC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B648C3B6-203D-4C57-A8FE-3F042380720D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="127">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -410,6 +410,12 @@
   </si>
   <si>
     <t>Today I went for blood donation camp to donate blood.</t>
+  </si>
+  <si>
+    <t>Today I explore the campus with my friends.</t>
+  </si>
+  <si>
+    <t>attended classes and completed the assigned work.</t>
   </si>
 </sst>
 </file>
@@ -4038,52 +4044,102 @@
         <v>124</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+    <row r="68" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="14">
+        <v>400</v>
+      </c>
+      <c r="C68" s="14">
+        <v>60</v>
+      </c>
+      <c r="D68" s="14">
+        <v>150</v>
+      </c>
+      <c r="E68" s="14">
+        <v>120</v>
+      </c>
+      <c r="F68" s="14">
+        <v>360</v>
+      </c>
+      <c r="G68" s="14">
+        <v>6</v>
+      </c>
+      <c r="H68" s="14">
+        <v>200</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+        <v>150</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="14">
+        <v>300</v>
+      </c>
+      <c r="C69" s="14">
+        <v>150</v>
+      </c>
+      <c r="D69" s="14">
+        <v>200</v>
+      </c>
+      <c r="E69" s="14">
+        <v>60</v>
+      </c>
+      <c r="F69" s="14">
+        <v>50</v>
+      </c>
+      <c r="G69" s="14">
+        <v>1</v>
+      </c>
+      <c r="H69" s="14">
+        <v>400</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
+      <c r="A70" s="13">
+        <v>46320</v>
+      </c>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B648C3B6-203D-4C57-A8FE-3F042380720D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4E26B8-494B-4025-A4CB-40098F0A2970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="130">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -416,6 +416,15 @@
   </si>
   <si>
     <t>attended classes and completed the assigned work.</t>
+  </si>
+  <si>
+    <t>Completed my oending works on weekend.</t>
+  </si>
+  <si>
+    <t>I completed the analytical task today.</t>
+  </si>
+  <si>
+    <t>today enjoyed a lot with friends.</t>
   </si>
 </sst>
 </file>
@@ -4136,73 +4145,143 @@
         <v>125</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="13">
         <v>46320</v>
       </c>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="B70" s="14">
+        <v>400</v>
+      </c>
+      <c r="C70" s="14">
+        <v>150</v>
+      </c>
+      <c r="D70" s="14">
+        <v>150</v>
+      </c>
+      <c r="E70" s="14">
+        <v>90</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>500</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+        <v>150</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="14">
+        <v>500</v>
+      </c>
+      <c r="C71" s="14">
+        <v>120</v>
+      </c>
+      <c r="D71" s="14">
+        <v>160</v>
+      </c>
+      <c r="E71" s="14">
+        <v>90</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>550</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>20</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="14">
+        <v>300</v>
+      </c>
+      <c r="C72" s="14">
+        <v>200</v>
+      </c>
+      <c r="D72" s="14">
+        <v>100</v>
+      </c>
+      <c r="E72" s="14">
+        <v>60</v>
+      </c>
+      <c r="F72" s="14">
+        <v>150</v>
+      </c>
+      <c r="G72" s="14">
+        <v>3</v>
+      </c>
+      <c r="H72" s="14">
+        <v>600</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4E26B8-494B-4025-A4CB-40098F0A2970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE009B59-1FE5-455B-8E30-C795961D4087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="131">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -425,6 +425,9 @@
   </si>
   <si>
     <t>today enjoyed a lot with friends.</t>
+  </si>
+  <si>
+    <t>Today I completed with my networking CA preparation.</t>
   </si>
 </sst>
 </file>
@@ -4284,48 +4287,94 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="14">
+        <v>350</v>
+      </c>
+      <c r="C73" s="14">
+        <v>100</v>
+      </c>
+      <c r="D73" s="14">
+        <v>150</v>
+      </c>
+      <c r="E73" s="14">
+        <v>120</v>
+      </c>
+      <c r="F73" s="14">
+        <v>150</v>
+      </c>
+      <c r="G73" s="14">
+        <v>3</v>
+      </c>
+      <c r="H73" s="14">
+        <v>400</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+    <row r="74" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="14">
+        <v>200</v>
+      </c>
+      <c r="C74" s="14">
+        <v>150</v>
+      </c>
+      <c r="D74" s="14">
+        <v>250</v>
+      </c>
+      <c r="E74" s="14">
+        <v>90</v>
+      </c>
+      <c r="F74" s="14">
+        <v>250</v>
+      </c>
+      <c r="G74" s="14">
+        <v>5</v>
+      </c>
+      <c r="H74" s="14">
+        <v>300</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>
